--- a/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
+++ b/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
@@ -7,16 +7,56 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="未匹配_工号" sheetId="1" r:id="rId1"/>
-    <sheet name="未匹配_供应商" sheetId="2" r:id="rId2"/>
-    <sheet name="未匹配_费用科目" sheetId="3" r:id="rId3"/>
+    <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
+    <sheet name="未匹配_工号" sheetId="2" r:id="rId2"/>
+    <sheet name="未匹配_供应商" sheetId="3" r:id="rId3"/>
+    <sheet name="未匹配_费用科目" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+  <si>
+    <t>必输字段</t>
+  </si>
+  <si>
+    <t>填充数</t>
+  </si>
+  <si>
+    <t>缺失数</t>
+  </si>
+  <si>
+    <t>总数</t>
+  </si>
+  <si>
+    <t>填充率</t>
+  </si>
+  <si>
+    <t>申请人工号</t>
+  </si>
+  <si>
+    <t>订单编号</t>
+  </si>
+  <si>
+    <t>收款方编码</t>
+  </si>
+  <si>
+    <t>费用项目编码</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>93.9%</t>
+  </si>
+  <si>
+    <t>97.9%</t>
+  </si>
   <si>
     <t>未匹配_经办人(工号)</t>
   </si>
@@ -473,27 +513,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>4373</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>4383</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>4383</v>
+      </c>
+      <c r="D3">
+        <v>4383</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>4116</v>
+      </c>
+      <c r="C4">
+        <v>267</v>
+      </c>
+      <c r="D4">
+        <v>4383</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>4293</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>4383</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -503,177 +608,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -683,27 +638,207 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
+++ b/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
@@ -8,16 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
-    <sheet name="未匹配_工号" sheetId="2" r:id="rId2"/>
-    <sheet name="未匹配_供应商" sheetId="3" r:id="rId3"/>
-    <sheet name="未匹配_费用科目" sheetId="4" r:id="rId4"/>
+    <sheet name="缺失_申请人工号" sheetId="2" r:id="rId2"/>
+    <sheet name="缺失_收款方编码" sheetId="3" r:id="rId3"/>
+    <sheet name="缺失_费用项目编码" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="286">
   <si>
     <t>必输字段</t>
   </si>
@@ -58,7 +58,43 @@
     <t>97.9%</t>
   </si>
   <si>
-    <t>未匹配_经办人(工号)</t>
+    <t>来源单据编号</t>
+  </si>
+  <si>
+    <t>泛微原表-经办人</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-163-0011</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-151-0025</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-163-0010</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-103-0017</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-163-0003</t>
+  </si>
+  <si>
+    <t>F1-V-386-0005</t>
+  </si>
+  <si>
+    <t>F1-V-386-0004</t>
+  </si>
+  <si>
+    <t>F1-V-386-0001</t>
+  </si>
+  <si>
+    <t>F1-C1-2025-009-0002</t>
+  </si>
+  <si>
+    <t>F1-C1-2025-009-0001</t>
+  </si>
+  <si>
+    <t>罗文静</t>
   </si>
   <si>
     <t>保琳</t>
@@ -67,121 +103,778 @@
     <t>王珊珊1</t>
   </si>
   <si>
-    <t>罗文静</t>
-  </si>
-  <si>
-    <t>未匹配_供应商(收款方编码)</t>
+    <t>泛微原表-供应商-文本</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-138-0014</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-035-0012</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-166-0006</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-017-0024</t>
+  </si>
+  <si>
+    <t>F1-B7-2026-035-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-035-0010</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-166-0005</t>
+  </si>
+  <si>
+    <t>F1-A1-2026-013-0005</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-131-0013</t>
+  </si>
+  <si>
+    <t>F1-C1-2026-005-0015</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-166-0004</t>
+  </si>
+  <si>
+    <t>F1-A1-2026-022-0010</t>
+  </si>
+  <si>
+    <t>F1-A1-2026-013-0004</t>
+  </si>
+  <si>
+    <t>F1-B9-2025-013-0050</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-017-0017</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-030-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-030-0008</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-030-0007</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0057</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-022-0044</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-166-0003</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-131-0009</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0141</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-166-0001</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0128</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0049</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0021</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0020</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0019</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0018</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0017</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0016</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0015</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0014</t>
+  </si>
+  <si>
+    <t>F1-B5-2026-002-021-0006</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-038-0052</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-038-0051</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0119</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0118</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0117</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0012</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0115</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0114</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0113</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0112</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-090-0031</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0111</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0110</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0109</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-016-0012</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0106</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-151-0009</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0037</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0036</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-102-0002</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0094</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-103-0009</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-071-0026</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0091</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0090</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0089</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0088</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-071-0025</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-003-0037</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0087</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0086</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0085</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0084</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0083</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0082</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0081</t>
+  </si>
+  <si>
+    <t>F1-Y2-2025-006-0004</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-083-0013</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-102-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-035-0004</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-035-0003</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-035-0002</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-071-0012</t>
+  </si>
+  <si>
+    <t>F1-A3-2025-002-0058</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-090-0010</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-313-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-038-0038</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0009</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0006</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0005</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0004</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0003</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0002</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-050-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-186-0101</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0054</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-277-0001</t>
+  </si>
+  <si>
+    <t>F1-A4-2026-042-0001</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-024-0008</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0052</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0051</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0050</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-021-0023</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-021-0022</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-021-0020</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-022-0016</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-071-0001</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0045</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0044</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0043</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0042</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0041</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0040</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0039</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-119-0088</t>
+  </si>
+  <si>
+    <t>F1-Y2-2026-009-0004</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0032</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0029</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0009</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0026</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-296-0007</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0025</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0024</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0023</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0019</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0018</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0017</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0016</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0015</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0014</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-008-0018</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0013</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-292-0006</t>
+  </si>
+  <si>
+    <t>F1-V-011-0076</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-296-0004</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-292-0005</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-312-0021</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-296-0003</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-067-0035</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-021-0005</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-021-0004</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-301-0008</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-301-0007</t>
+  </si>
+  <si>
+    <t>F1-A3-2026-001-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2026-032-0001</t>
+  </si>
+  <si>
+    <t>F1-B1-2025-009-0099</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-027-0145</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-301-0005</t>
+  </si>
+  <si>
+    <t>F1-B9-2025-007-0156</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0021</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0019</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0018</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0017</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0016</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-198-0015</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-314-0001</t>
+  </si>
+  <si>
+    <t>F1-B2-2025-119-0084</t>
+  </si>
+  <si>
+    <t>F1-A3-2025-003-0354</t>
+  </si>
+  <si>
+    <t>F1-A3-2025-003-0353</t>
+  </si>
+  <si>
+    <t>F1-A3-2025-003-0352</t>
+  </si>
+  <si>
+    <t>浙江不古文化创意有限公司</t>
+  </si>
+  <si>
+    <t>上海集梦芽文化发展有限公司</t>
+  </si>
+  <si>
+    <t>广西佳絮文化艺术传播有限责任公司</t>
+  </si>
+  <si>
+    <t>首都医科大学附属北京康复医院</t>
+  </si>
+  <si>
+    <t>福建汇道文化传播有限公司</t>
+  </si>
+  <si>
+    <t>KHURTS ARTSSED</t>
+  </si>
+  <si>
+    <t>贵州陌客视觉科技有限公司</t>
+  </si>
+  <si>
+    <t>格拉夫节能制品(南京)有限公司</t>
+  </si>
+  <si>
+    <t>Fernando Halim</t>
+  </si>
+  <si>
+    <t>北京时代丽影文化传媒有限公司</t>
+  </si>
+  <si>
+    <t>上海扬培文化发展有限公司成都分公司</t>
+  </si>
+  <si>
+    <t>上海千伽装饰工程有限公司</t>
+  </si>
+  <si>
+    <t>深圳市鹿跃晴光文化科技有限公司</t>
   </si>
   <si>
     <t>Crushed Wines Limited</t>
   </si>
   <si>
-    <t>Fernando Halim</t>
+    <t>广州市迪凡工艺品有限公司</t>
+  </si>
+  <si>
+    <t>江苏淞兴律师事务所</t>
+  </si>
+  <si>
+    <t>北京宏胜友文化传媒有限公司</t>
+  </si>
+  <si>
+    <t>PUNGKY FIRMAN NINDI</t>
+  </si>
+  <si>
+    <t>宁波励时科技有限公司</t>
+  </si>
+  <si>
+    <t>长沙县泉塘街道展卓租凭服务部(个体工商户)</t>
+  </si>
+  <si>
+    <t>江宁区阿浙摄影工作室</t>
   </si>
   <si>
     <t>GARUDA PRODUKSI KREATIF</t>
   </si>
   <si>
-    <t>KHURTS ARTSSED</t>
+    <t>东莞安信玩具有限公司</t>
   </si>
   <si>
     <t>N E X T G E N S T U D I O</t>
   </si>
   <si>
+    <t>途居露营投资管理股份有限公司</t>
+  </si>
+  <si>
+    <t>上海市国库收付中心</t>
+  </si>
+  <si>
     <t>PT Monarch International Kreasi</t>
   </si>
   <si>
-    <t>PUNGKY FIRMAN NINDI</t>
+    <t>安付宝支付有限公司客户备付金</t>
+  </si>
+  <si>
+    <t>SK telecom CS T1 Co., Ltd.</t>
+  </si>
+  <si>
+    <t>上海佳玲影像服务有限公司</t>
   </si>
   <si>
     <t>Prismax</t>
   </si>
   <si>
-    <t>SK telecom CS T1 Co., Ltd.</t>
-  </si>
-  <si>
-    <t>上海佳玲影像服务有限公司</t>
-  </si>
-  <si>
-    <t>上海千伽装饰工程有限公司</t>
-  </si>
-  <si>
-    <t>上海市国库收付中心</t>
-  </si>
-  <si>
-    <t>上海扬培文化发展有限公司成都分公司</t>
+    <t>澄迈源福餐饮管理有限公司（南海东坡）</t>
   </si>
   <si>
     <t>上海蓝护护理服务有限公司</t>
   </si>
   <si>
-    <t>上海集梦芽文化发展有限公司</t>
-  </si>
-  <si>
-    <t>东莞安信玩具有限公司</t>
-  </si>
-  <si>
-    <t>北京宏胜友文化传媒有限公司</t>
-  </si>
-  <si>
-    <t>北京时代丽影文化传媒有限公司</t>
-  </si>
-  <si>
-    <t>宁波励时科技有限公司</t>
-  </si>
-  <si>
-    <t>安付宝支付有限公司客户备付金</t>
-  </si>
-  <si>
-    <t>广州市迪凡工艺品有限公司</t>
-  </si>
-  <si>
-    <t>广西佳絮文化艺术传播有限责任公司</t>
-  </si>
-  <si>
-    <t>格拉夫节能制品(南京)有限公司</t>
-  </si>
-  <si>
-    <t>江宁区阿浙摄影工作室</t>
-  </si>
-  <si>
-    <t>江苏淞兴律师事务所</t>
-  </si>
-  <si>
-    <t>浙江不古文化创意有限公司</t>
-  </si>
-  <si>
-    <t>深圳市鹿跃晴光文化科技有限公司</t>
-  </si>
-  <si>
-    <t>澄迈源福餐饮管理有限公司（南海东坡）</t>
-  </si>
-  <si>
-    <t>福建汇道文化传播有限公司</t>
-  </si>
-  <si>
-    <t>贵州陌客视觉科技有限公司</t>
-  </si>
-  <si>
-    <t>途居露营投资管理股份有限公司</t>
-  </si>
-  <si>
-    <t>长沙县泉塘街道展卓租凭服务部(个体工商户)</t>
-  </si>
-  <si>
-    <t>首都医科大学附属北京康复医院</t>
-  </si>
-  <si>
-    <t>未匹配_预算科目(费用项目)</t>
+    <t>泛微原表-预算科目</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0059</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0058</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0057</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0022</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0019</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0072</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-023-0008</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0055</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0003</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0019</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0017</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0018</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0046</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0042</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0041</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0055</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0016</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0001</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0011</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-007-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0007</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0029</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0028</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0027</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0048</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0005</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0004</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0003</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0185</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0184</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0005</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0018</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0017</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0006</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0006</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0023</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0004</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0183</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-010-0037</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-010-0036</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-023-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0014</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0180</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0179</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0011</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0009</t>
+  </si>
+  <si>
+    <t>F1-A4-2025-016-0189</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-014-0038</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-006-0051</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR632能耗费/AR6321办公房屋</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR633水费/AR6331办公房屋</t>
   </si>
   <si>
     <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR631电费/AR6311办公房屋</t>
-  </si>
-  <si>
-    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR632能耗费/AR6321办公房屋</t>
-  </si>
-  <si>
-    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR633水费/AR6331办公房屋</t>
   </si>
 </sst>
 </file>
@@ -608,27 +1301,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -638,177 +1399,912 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>129</v>
+      </c>
+      <c r="B102" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>130</v>
+      </c>
+      <c r="B103" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>50</v>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>157</v>
+      </c>
+      <c r="B131" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>160</v>
+      </c>
+      <c r="B134" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>165</v>
+      </c>
+      <c r="B139" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>169</v>
+      </c>
+      <c r="B143" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>170</v>
+      </c>
+      <c r="B144" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>171</v>
+      </c>
+      <c r="B145" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>179</v>
+      </c>
+      <c r="B153" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -818,27 +2314,735 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>218</v>
+      </c>
+      <c r="B2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>218</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>218</v>
+      </c>
+      <c r="B4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B11" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>228</v>
+      </c>
+      <c r="B16" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>239</v>
+      </c>
+      <c r="B33" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B34" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>241</v>
+      </c>
+      <c r="B35" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>243</v>
+      </c>
+      <c r="B37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>243</v>
+      </c>
+      <c r="B38" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>244</v>
+      </c>
+      <c r="B39" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>244</v>
+      </c>
+      <c r="B40" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>246</v>
+      </c>
+      <c r="B43" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>247</v>
+      </c>
+      <c r="B45" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>248</v>
+      </c>
+      <c r="B46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>249</v>
+      </c>
+      <c r="B47" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>250</v>
+      </c>
+      <c r="B48" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>253</v>
+      </c>
+      <c r="B51" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>254</v>
+      </c>
+      <c r="B52" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>255</v>
+      </c>
+      <c r="B53" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>258</v>
+      </c>
+      <c r="B56" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>259</v>
+      </c>
+      <c r="B57" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>260</v>
+      </c>
+      <c r="B58" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>261</v>
+      </c>
+      <c r="B59" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>262</v>
+      </c>
+      <c r="B60" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>262</v>
+      </c>
+      <c r="B61" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>262</v>
+      </c>
+      <c r="B62" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>263</v>
+      </c>
+      <c r="B63" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>264</v>
+      </c>
+      <c r="B64" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>265</v>
+      </c>
+      <c r="B65" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>266</v>
+      </c>
+      <c r="B66" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>267</v>
+      </c>
+      <c r="B67" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>268</v>
+      </c>
+      <c r="B68" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>269</v>
+      </c>
+      <c r="B69" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>270</v>
+      </c>
+      <c r="B70" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>270</v>
+      </c>
+      <c r="B71" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>270</v>
+      </c>
+      <c r="B72" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>271</v>
+      </c>
+      <c r="B73" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>271</v>
+      </c>
+      <c r="B75" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>272</v>
+      </c>
+      <c r="B76" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>272</v>
+      </c>
+      <c r="B77" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>273</v>
+      </c>
+      <c r="B78" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>274</v>
+      </c>
+      <c r="B79" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>274</v>
+      </c>
+      <c r="B80" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>275</v>
+      </c>
+      <c r="B81" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>277</v>
+      </c>
+      <c r="B83" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>277</v>
+      </c>
+      <c r="B84" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>278</v>
+      </c>
+      <c r="B85" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>278</v>
+      </c>
+      <c r="B86" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>279</v>
+      </c>
+      <c r="B87" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>279</v>
+      </c>
+      <c r="B88" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>280</v>
+      </c>
+      <c r="B89" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>281</v>
+      </c>
+      <c r="B90" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>282</v>
+      </c>
+      <c r="B91" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
+++ b/output/ap_payment_opening/未匹配清单_应付期初_20260614.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="必输字段未达100%" sheetId="1" r:id="rId1"/>
     <sheet name="缺失_收款方编码" sheetId="2" r:id="rId2"/>
+    <sheet name="缺失_费用项目编码" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="271">
   <si>
     <t>必输字段</t>
   </si>
@@ -47,6 +48,9 @@
     <t>93.9%</t>
   </si>
   <si>
+    <t>97.9%</t>
+  </si>
+  <si>
     <t>来源单据编号</t>
   </si>
   <si>
@@ -618,6 +622,213 @@
   </si>
   <si>
     <t>上海蓝护护理服务有限公司</t>
+  </si>
+  <si>
+    <t>泛微原表-预算科目</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0059</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0058</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0057</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0022</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0019</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0072</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-023-0008</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0055</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0003</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0019</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0017</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0018</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0046</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0042</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0041</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0055</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0016</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-038-0001</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0013</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0011</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-007-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0007</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0029</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0028</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0027</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0048</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0005</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-040-0004</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0003</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-021-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0021</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0009</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0185</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0184</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-004-0005</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0018</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-001-0017</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0006</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-016-0006</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-011-0023</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0004</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0183</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-010-0037</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-010-0036</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-023-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2026-020-0002</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0014</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0180</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-002-0179</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0012</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0011</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-013-0009</t>
+  </si>
+  <si>
+    <t>F1-A4-2025-016-0189</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-014-0038</t>
+  </si>
+  <si>
+    <t>F1-A2-2025-006-0051</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR632能耗费/AR6321办公房屋</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR633水费/AR6331办公房屋</t>
+  </si>
+  <si>
+    <t>AR日常运营费用/AR6房屋租赁/AR63能源消耗/AR631电费/AR6311办公房屋</t>
   </si>
 </sst>
 </file>
@@ -1008,16 +1219,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>4293</v>
       </c>
       <c r="C4">
-        <v>4383</v>
+        <v>90</v>
       </c>
       <c r="D4">
         <v>4383</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1032,907 +1243,1645 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B131" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B134" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B139" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B140" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B143" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B144" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B145" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B153" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>167</v>
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B91"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>226</v>
+      </c>
+      <c r="B35" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>228</v>
+      </c>
+      <c r="B38" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>229</v>
+      </c>
+      <c r="B41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>231</v>
+      </c>
+      <c r="B44" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>232</v>
+      </c>
+      <c r="B45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>234</v>
+      </c>
+      <c r="B47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>235</v>
+      </c>
+      <c r="B48" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>236</v>
+      </c>
+      <c r="B49" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>237</v>
+      </c>
+      <c r="B50" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>242</v>
+      </c>
+      <c r="B55" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>243</v>
+      </c>
+      <c r="B56" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>244</v>
+      </c>
+      <c r="B57" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>245</v>
+      </c>
+      <c r="B58" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>246</v>
+      </c>
+      <c r="B59" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>247</v>
+      </c>
+      <c r="B60" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>247</v>
+      </c>
+      <c r="B62" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>248</v>
+      </c>
+      <c r="B63" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>249</v>
+      </c>
+      <c r="B64" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>250</v>
+      </c>
+      <c r="B65" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>251</v>
+      </c>
+      <c r="B66" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>252</v>
+      </c>
+      <c r="B67" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>253</v>
+      </c>
+      <c r="B68" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>254</v>
+      </c>
+      <c r="B69" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>255</v>
+      </c>
+      <c r="B72" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>256</v>
+      </c>
+      <c r="B73" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>256</v>
+      </c>
+      <c r="B74" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>257</v>
+      </c>
+      <c r="B76" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>257</v>
+      </c>
+      <c r="B77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>258</v>
+      </c>
+      <c r="B78" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>259</v>
+      </c>
+      <c r="B79" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>259</v>
+      </c>
+      <c r="B80" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>260</v>
+      </c>
+      <c r="B81" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>261</v>
+      </c>
+      <c r="B82" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>262</v>
+      </c>
+      <c r="B83" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>262</v>
+      </c>
+      <c r="B84" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>263</v>
+      </c>
+      <c r="B85" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>263</v>
+      </c>
+      <c r="B86" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>264</v>
+      </c>
+      <c r="B87" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B88" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>265</v>
+      </c>
+      <c r="B89" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>266</v>
+      </c>
+      <c r="B90" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>267</v>
+      </c>
+      <c r="B91" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
